--- a/artfynd/A 35844-2021 artfynd.xlsx
+++ b/artfynd/A 35844-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 35844-2021 artfynd.xlsx
+++ b/artfynd/A 35844-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>94800840</v>
+        <v>94801501</v>
       </c>
       <c r="B2" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97231</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,36 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100526</v>
+        <v>2869</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Avesta, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578114.130457453</v>
+        <v>578082</v>
       </c>
       <c r="R2" t="n">
-        <v>6691466.12155168</v>
+        <v>6691533</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -753,7 +747,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,14 +757,14 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="b">
         <v>0</v>
@@ -778,65 +772,58 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mariapaz Ojeda</t>
+          <t>Kim Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mariapaz Ojeda</t>
+          <t>Kim Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>94802014</v>
+        <v>94976031</v>
       </c>
       <c r="B3" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79351</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6434</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Avesta, Dlr</t>
+          <t>Byvalla, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578133.5591007833</v>
+        <v>578051</v>
       </c>
       <c r="R3" t="n">
-        <v>6691508.123693501</v>
+        <v>6691604</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -863,29 +850,29 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-07-10</t>
+          <t>2021-07-19</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>21:08</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-07-10</t>
+          <t>2021-07-19</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>21:08</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG3" t="b">
         <v>0</v>
@@ -893,27 +880,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mariapaz Ojeda</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mariapaz Ojeda</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>94801501</v>
+        <v>94802014</v>
       </c>
       <c r="B4" t="n">
-        <v>93868</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -921,36 +903,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2869</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Avesta, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578082.429931665</v>
+        <v>578134</v>
       </c>
       <c r="R4" t="n">
-        <v>6691533.758523043</v>
+        <v>6691508</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -982,7 +965,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>20:40</t>
+          <t>21:08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -992,7 +975,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>20:40</t>
+          <t>21:08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1007,27 +990,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Andersson</t>
+          <t>Mariapaz Ojeda</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Andersson</t>
+          <t>Mariapaz Ojeda</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>94801940</v>
+        <v>94800840</v>
       </c>
       <c r="B5" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1035,44 +1013,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219790</v>
+        <v>100526</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Byvalla, Dlr</t>
+          <t>Avesta, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>578091.1246136333</v>
+        <v>578114</v>
       </c>
       <c r="R5" t="n">
-        <v>6691567.608498921</v>
+        <v>6691466</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1104,7 +1075,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1114,14 +1085,14 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG5" t="b">
         <v>0</v>
@@ -1129,49 +1100,44 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Andersson</t>
+          <t>Mariapaz Ojeda</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Andersson</t>
+          <t>Mariapaz Ojeda</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>94975882</v>
+        <v>95089123</v>
       </c>
       <c r="B6" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219790</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1179,22 +1145,23 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Byvalla, Dlr</t>
+          <t>Avesta, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>578109.6573285174</v>
+        <v>578136</v>
       </c>
       <c r="R6" t="n">
-        <v>6691605.134754044</v>
+        <v>6691510</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1221,22 +1188,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-07-19</t>
+          <t>2021-07-25</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>19:47</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-07-19</t>
+          <t>2021-07-25</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>19:47</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1251,27 +1218,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Kim Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Kim Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>94975981</v>
+        <v>94975478</v>
       </c>
       <c r="B7" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58817</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1279,36 +1241,45 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>208249</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Byvalla, Dlr</t>
+          <t>Avesta, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>578050.6668432502</v>
+        <v>578230</v>
       </c>
       <c r="R7" t="n">
-        <v>6691604.363364403</v>
+        <v>6691521</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1340,7 +1311,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1350,14 +1321,14 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG7" t="b">
         <v>0</v>
@@ -1365,27 +1336,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Mariapaz Ojeda</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Mariapaz Ojeda</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>94976031</v>
+        <v>94975275</v>
       </c>
       <c r="B8" t="n">
-        <v>77532</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58815</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1393,35 +1359,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6434</v>
+        <v>208250</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Byvalla, Dlr</t>
+          <t>Avesta, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>578050.6668432502</v>
+        <v>578242</v>
       </c>
       <c r="R8" t="n">
-        <v>6691604.363364403</v>
+        <v>6691517</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1451,19 +1419,9 @@
           <t>2021-07-19</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>17:42</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2021-07-19</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>17:42</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1478,49 +1436,44 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>fanny westling</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>fanny westling</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>95089123</v>
+        <v>94801940</v>
       </c>
       <c r="B9" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>219790</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1528,23 +1481,22 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Avesta, Dlr</t>
+          <t>Byvalla, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>578135.5204094676</v>
+        <v>578091</v>
       </c>
       <c r="R9" t="n">
-        <v>6691509.155936676</v>
+        <v>6691568</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1571,22 +1523,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2021-07-25</t>
+          <t>2021-07-10</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>19:47</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2021-07-25</t>
+          <t>2021-07-10</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>19:47</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1610,6 +1562,232 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>94975882</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Byvalla, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>578110</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6691605</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Avesta</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>By</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2021-07-19</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>17:36</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2021-07-19</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>17:36</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>94975981</v>
+      </c>
+      <c r="B11" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Byvalla, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>578051</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6691604</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Avesta</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>By</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2021-07-19</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>17:39</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2021-07-19</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>17:39</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
